--- a/Templates/DepartmentReportTemplate.xlsx
+++ b/Templates/DepartmentReportTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Прил.3 часть 1" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Прил.3 часть 1'!$A$1:$I$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Прил.3 часть 2'!$A$1:$J$19</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>Приложение 3</t>
   </si>
@@ -66,6 +66,12 @@
     <t>Начальник отдела  _________________________________</t>
   </si>
   <si>
+    <t>&lt;workName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;specialCode&gt;</t>
+  </si>
+  <si>
     <t>&lt;programName&gt;</t>
   </si>
   <si>
@@ -91,6 +97,27 @@
   </si>
   <si>
     <t>Начальник отдела _________________________________</t>
+  </si>
+  <si>
+    <t>&lt;day1&gt;</t>
+  </si>
+  <si>
+    <t>&lt;day2&gt;</t>
+  </si>
+  <si>
+    <t>&lt;day3&gt;</t>
+  </si>
+  <si>
+    <t>&lt;day4&gt;</t>
+  </si>
+  <si>
+    <t>&lt;day5&gt;</t>
+  </si>
+  <si>
+    <t>&lt;day6&gt;</t>
+  </si>
+  <si>
+    <t>&lt;day7&gt;</t>
   </si>
   <si>
     <t>&lt;periodStart&gt;</t>
@@ -177,6 +204,9 @@
       </rPr>
       <t xml:space="preserve">(согласно Классификатору ХХ-ХХХХ-ХХХ) </t>
     </r>
+  </si>
+  <si>
+    <t>Филиал АО "ЦЭНКИ" - Космический центр "Южный"</t>
   </si>
 </sst>
 </file>
@@ -574,43 +604,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -623,6 +653,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -973,7 +1006,7 @@
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="30" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="30"/>
       <c r="E4" s="30"/>
@@ -1000,7 +1033,9 @@
         <v>4</v>
       </c>
       <c r="B6" s="29"/>
-      <c r="C6" s="33"/>
+      <c r="C6" s="33" t="s">
+        <v>37</v>
+      </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
       <c r="F6" s="33"/>
@@ -1027,7 +1062,7 @@
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -1055,7 +1090,7 @@
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
@@ -1093,7 +1128,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C13" s="34" t="s">
         <v>11</v>
@@ -1111,34 +1146,50 @@
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I14" s="34"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="A15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19">
+        <v>0</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0</v>
+      </c>
+      <c r="F15" s="19">
+        <v>0</v>
+      </c>
+      <c r="G15" s="19">
+        <v>0</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0</v>
+      </c>
       <c r="I15" s="20">
         <f>SUM(C15:H15)</f>
         <v>0</v>
@@ -1233,20 +1284,20 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="43"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -1265,133 +1316,135 @@
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
     </row>
     <row r="12" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="46"/>
+      <c r="A12" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="41"/>
       <c r="C12" s="21" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -1404,10 +1457,10 @@
       <c r="A13" s="8"/>
       <c r="B13" s="7"/>
       <c r="C13" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1429,47 +1482,79 @@
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="47"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="37"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
+      <c r="F16" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="J16" s="23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="20">
+        <v>0</v>
+      </c>
+      <c r="D17" s="20">
+        <v>0</v>
+      </c>
+      <c r="E17" s="20">
+        <v>0</v>
+      </c>
+      <c r="F17" s="20">
+        <v>0</v>
+      </c>
+      <c r="G17" s="20">
+        <v>0</v>
+      </c>
+      <c r="H17" s="20">
+        <v>0</v>
+      </c>
+      <c r="I17" s="20">
+        <v>0</v>
+      </c>
       <c r="J17" s="25">
         <f>SUM(C17:I17)</f>
         <v>0</v>
@@ -1492,17 +1577,23 @@
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
+      <c r="E19" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C10:J10"/>
     <mergeCell ref="E19:J19"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A2:F2"/>
@@ -1516,12 +1607,6 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C10:J10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" r:id="rId1"/>
